--- a/inspection_forms/036_crane_inspection_checklist--inspection_forms.xlsx
+++ b/inspection_forms/036_crane_inspection_checklist--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>crane_inspection_checklist_1</t>
+          <t>Crane Inspection Checklist Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>checklist_items</t>
+          <t>Inspection Checklist for Crane Model</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>inspection_frequency</t>
+          <t>Inspection Checklist for Crane Type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>inspection_status</t>
+          <t>Inspection Checklist for Crane Location</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>inspection_date</t>
+          <t>What is the current inspection status?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>inspection_by</t>
+          <t>What is the last inspection date?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Who performed the last inspection?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>crane_model</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>Crane Model</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,20 +732,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>inspection_frequency</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>inspection_date</t>
+          <t>Inspection Frequency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,13 +778,151 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>inspection_by</t>
+          <t>Crane Inspection Checklist 12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>crane_inspection_checklist_13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Last Inspection Date</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>crane_inspection_checklist_14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Last Inspected By</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>crane_inspection_checklist_15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Inspection Type</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>crane_inspection_checklist_16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Crane Inspection Checklist 16</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>crane_inspection_checklist_17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Crane Inspection Checklist 17</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>crane_inspection_checklist_18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Last Inspection Frequency</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -802,9 +940,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,102 +965,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>crane_inspection_checklist_2_choices</t>
+          <t>crane_inspection_checklist_5_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>crane_inspection_checklist_2_choices</t>
+          <t>crane_inspection_checklist_5_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>crane_inspection_checklist_2_choices</t>
+          <t>crane_inspection_checklist_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>crane_inspection_checklist_4_choices</t>
+          <t>crane_inspection_checklist_15_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>Annual</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>crane_inspection_checklist_4_choices</t>
+          <t>crane_inspection_checklist_15_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>periodic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>Periodic</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>crane_inspection_checklist_4_choices</t>
+          <t>crane_inspection_checklist_15_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>special</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>Special</t>
         </is>
       </c>
     </row>
